--- a/Assets/_TankRes/excel/const.xlsx
+++ b/Assets/_TankRes/excel/const.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="const" sheetId="1" r:id="rId1"/>
@@ -1044,11 +1044,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="25.0083333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.0083333333333" customWidth="1"/>
-    <col min="3" max="3" width="16.3416666666667" customWidth="1"/>
+    <col min="1" max="1" width="25.0092592592593" customWidth="1"/>
+    <col min="2" max="2" width="11.0092592592593" customWidth="1"/>
+    <col min="3" max="3" width="16.3425925925926" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.25" customHeight="1" spans="1:3">
@@ -1105,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>

--- a/Assets/_TankRes/excel/const.xlsx
+++ b/Assets/_TankRes/excel/const.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="const" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>唯一标识</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>初始坦克类型ID</t>
+  </si>
+  <si>
+    <t>EnemyGenerateMaxCount</t>
+  </si>
+  <si>
+    <t>敌方坦克地图中共存的最大个数</t>
+  </si>
+  <si>
+    <t>EnemyGenerateIntervalMS</t>
+  </si>
+  <si>
+    <t>敌方坦克生成频率ms</t>
   </si>
 </sst>
 </file>
@@ -1044,11 +1056,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="25.0092592592593" customWidth="1"/>
-    <col min="2" max="2" width="11.0092592592593" customWidth="1"/>
-    <col min="3" max="3" width="16.3425925925926" customWidth="1"/>
+    <col min="1" max="1" width="25.0083333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.0083333333333" customWidth="1"/>
+    <col min="3" max="3" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.25" customHeight="1" spans="1:3">
@@ -1112,14 +1124,26 @@
       </c>
     </row>
     <row r="7" ht="30.5" customHeight="1" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" ht="30.5" customHeight="1" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/_TankRes/excel/const.xlsx
+++ b/Assets/_TankRes/excel/const.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="const" sheetId="1" r:id="rId1"/>
